--- a/Documents/BusinessAnalysis/coface/评分卡匹配规则说明.xlsx
+++ b/Documents/BusinessAnalysis/coface/评分卡匹配规则说明.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28260" windowHeight="14120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="评分卡类型与匹配规则" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,34 +12,191 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coface指标映射" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="定性值映射" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整流程" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待确认与历史变更" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="23">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <sz val="12"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
@@ -49,11 +205,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000078D4"/>
+        <fgColor rgb="FF0078D4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -61,9 +404,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -73,8 +658,56 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -427,7 +1060,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -438,16 +1070,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="53.7692307692308" customWidth="1" min="1" max="1"/>
+    <col width="37.7692307692308" customWidth="1" min="2" max="2"/>
+    <col width="25.3076923076923" customWidth="1" min="3" max="3"/>
+    <col width="35.1538461538462" customWidth="1" min="4" max="4"/>
+    <col width="36.6153846153846" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="17.6" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>表1：评分卡类型概览（PRD 共 7 种）</t>
@@ -616,7 +1248,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="17.6" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
           <t>表2：匹配因子（评分卡类型由输入因子决定）</t>
@@ -653,7 +1285,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>salesorder 表中存在该客户订单记录</t>
+          <t>销售订单表中存在该客户订单记录</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -675,7 +1307,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>salesorder 表中无该客户订单记录</t>
+          <t>销售订单表中无该客户订单记录</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -697,7 +1329,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>mcs_accountcategory</t>
+          <t>客户类别</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -719,7 +1351,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>mcs_accountcategory</t>
+          <t>客户类别</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -741,7 +1373,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>mcs_accountcategory</t>
+          <t>客户类别</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -763,7 +1395,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>mcs_accountlevel</t>
+          <t>客户级别</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -785,7 +1417,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mcs_accountlevel</t>
+          <t>客户级别</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -807,7 +1439,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>mcs_accountlevel</t>
+          <t>客户级别</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -829,7 +1461,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>mcs_accountlevel</t>
+          <t>客户级别</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -851,7 +1483,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>mcs_accounttype</t>
+          <t>客户类型</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -873,7 +1505,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>mcs_accounttype</t>
+          <t>客户类型</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -887,7 +1519,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="17.6" customHeight="1">
       <c r="A25" s="1" t="inlineStr">
         <is>
           <t>表3：匹配结果速查表</t>
@@ -897,12 +1529,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>客户类别(category)</t>
+          <t>客户类别</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>客户级别(level)</t>
+          <t>客户级别</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1128,7 +1760,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>accounttype=1 (Individual Account)</t>
+          <t>客户类型=1（Individual Account）</t>
         </is>
       </c>
     </row>
@@ -1236,18 +1868,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="104.692307692308" customWidth="1" min="1" max="1"/>
+    <col width="28.5384615384615" customWidth="1" min="2" max="2"/>
+    <col width="12.7692307692308" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="17.6" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Account.mcs_accountcategory（客户类别）</t>
+          <t>客户表 - 客户类别</t>
         </is>
       </c>
     </row>
@@ -1433,10 +2065,10 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="17.6" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Account.mcs_accountlevel（客户级别）</t>
+          <t>客户表 - 客户级别</t>
         </is>
       </c>
     </row>
@@ -1517,10 +2149,10 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="17.6" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Account.mcs_dealerrank（经销商分级，当前代码未用于评分卡匹配，仅用于客户等级展示）</t>
+          <t>客户表 - 经销商分级（当前代码未用于评分卡匹配，仅用于客户等级展示）</t>
         </is>
       </c>
     </row>
@@ -1626,10 +2258,10 @@
       </c>
       <c r="D28" t="inlineStr"/>
     </row>
-    <row r="30">
+    <row r="30" ht="17.6" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>mcs_credit_scoringcard.mcs_categoryid（评分卡类型）</t>
+          <t>客户评分卡配置表 - 评分卡类型</t>
         </is>
       </c>
     </row>
@@ -1727,14 +2359,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="34.3846153846154" customWidth="1" min="1" max="1"/>
+    <col width="38.5384615384615" customWidth="1" min="2" max="2"/>
+    <col width="179.153846153846" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="17.6" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>评分项目分档配置与算分规则</t>
@@ -1771,7 +2403,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>同一 mcs_categoryid + 同一评分项目下，支持配置多行评分卡记录，用于覆盖不同的取值区间或定性枚举值</t>
+          <t>同一评分卡类型 + 同一评分项目下，支持配置多行评分卡记录，用于覆盖不同的取值区间或定性枚举值</t>
         </is>
       </c>
     </row>
@@ -1783,12 +2415,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>定量区间语义：左闭右开 [min, max)</t>
+          <t>定量区间语义：左闭右开 [定量最小值, 定量最大值)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>最小值 mcs_minvalue 包含在本分档内；最大值 mcs_maxvalue 不包含；要求 mcs_minvalue &lt; mcs_maxvalue</t>
+          <t>定量最小值（含）包含在本分档内；定量最大值（不含）不包含；要求定量最小值 &lt; 定量最大值</t>
         </is>
       </c>
     </row>
@@ -1805,7 +2437,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>定性分档通过 mcs_listvalue 存储的原始枚举值（如 L、M、H）进行匹配，匹配时不区分大小写</t>
+          <t>定性分档通过定性项目值存储的原始枚举值（如 L、M、H）进行匹配，匹配时不区分大小写</t>
         </is>
       </c>
     </row>
@@ -1817,7 +2449,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>赋分 mcs_weight 允许为负数</t>
+          <t>赋分允许为负数</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1839,7 +2471,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>一个客户标签记录只会命中同一评分项目下的一个分档，得分为对应分档的 mcs_weight</t>
+          <t>一个客户标签记录只会命中同一评分项目下的一个分档，得分为对应分档的赋分</t>
         </is>
       </c>
     </row>
@@ -1856,7 +2488,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>复核定量值（mcs_itemintvalue2）落在某一行 [min, max) 区间内即命中该行；若有多行满足，按数据库返回顺序取第一行</t>
+          <t>复核定量指标落在某一行 [定量最小值, 定量最大值) 区间内即命中该行；若有多行满足，按数据库返回顺序取第一行</t>
         </is>
       </c>
     </row>
@@ -1873,7 +2505,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>复核定性值（mcs_itemtxtvalue2）等于某一行 mcs_listvalue（忽略大小写）时命中；空字符串与 O 视为缺失值，不命中任何分档</t>
+          <t>复核定性指标等于某一行定性项目值（忽略大小写）时命中；空字符串与 O 视为缺失值，不命中任何分档</t>
         </is>
       </c>
     </row>
@@ -1924,7 +2556,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>同一 category + 评分项目下，不能存在两行配置相同的 mcs_listvalue（Create/Update PreOperation 阻断）</t>
+          <t>同一评分卡类型 + 评分项目下，不能存在两行配置相同的定性项目值（Create/Update PreOperation 阻断）</t>
         </is>
       </c>
     </row>
@@ -1941,7 +2573,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>同一 category + 评分项目下，任意两行的 [min, max) 区间不能重叠</t>
+          <t>同一评分卡类型 + 评分项目下，任意两行的 [定量最小值, 定量最大值) 区间不能重叠</t>
         </is>
       </c>
     </row>
@@ -1958,7 +2590,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mcs_minvalue &lt; mcs_maxvalue，重复或重叠时保存被阻断并返回错误信息</t>
+          <t>要求定量最小值 &lt; 定量最大值，重复或重叠时保存被阻断并返回错误信息</t>
         </is>
       </c>
     </row>
@@ -1974,15 +2606,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="109.605769230769" customWidth="1" min="1" max="1"/>
+    <col width="19.2307692307692" customWidth="1" min="2" max="2"/>
+    <col width="92.69230769230769" customWidth="1" min="3" max="3"/>
+    <col width="21.0769230769231" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="17.6" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>URBA360 接口指标映射</t>
@@ -2209,7 +2841,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="17.6" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
           <t>Full Report 接口指标映射</t>
@@ -2304,10 +2936,10 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="17.6" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Coface 财务指标国家配置表（mcs_coface_financial_indicator）字段说明</t>
+          <t>Coface 财务指标国家配置表字段说明</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2963,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mcs_countrycode</t>
+          <t>国家代码</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2348,7 +2980,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mcs_indicatorname</t>
+          <t>指标名称</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2365,7 +2997,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mcs_typevalue</t>
+          <t>Coface类型编码</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2382,7 +3014,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mcs_priority</t>
+          <t>匹配优先级</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2399,7 +3031,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mcs_indicatortype</t>
+          <t>取数位置</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2416,7 +3048,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mcs_formulafallback</t>
+          <t>兜底计算公式</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2442,7 +3074,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A2:H18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -2454,7 +3086,7 @@
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="2">
+    <row r="2" ht="17.6" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>国别风险（CountryRisk）</t>
@@ -2806,14 +3438,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="110" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="17.6" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>从数据集成到审批反写的完整流程</t>
@@ -2884,7 +3516,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>取值来源：评估记录的客户字段（mcs_accountid）→ 客户表；国家代码（mcs_countrycode）；科法斯客户代码（实际从客户主数据表带出）</t>
+          <t>取值来源：评估记录的客户编码字段 → 客户表；国家编码；科法斯客户代码（实际从客户主数据表带出）</t>
         </is>
       </c>
     </row>
@@ -2969,7 +3601,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>按评分项目数据来源（mcs_source）判断：外部指标 → Coface 取值；内部指标 → 生成空标签待人工补录</t>
+          <t>按评分项目内外部判断：外部指标 → Coface 取值；内部指标 → 生成空标签待人工补录</t>
         </is>
       </c>
     </row>
@@ -3140,147 +3772,6 @@
       <c r="C20" t="inlineStr">
         <is>
           <t>BPP状态=Rejected：状态→16 审批未通过，不回写客户主数据</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>待确认问题</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>待确认问题</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>个人客户（I级）识别：当前暂用 accountcategory=20 + accountlevel=1 识别，是否正确？</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>S/A/B/C 映射关系：Diamond(4)=S, Gold(3)=A, Silver(2)=B, Other(1)=C，是否正确？</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>mcs_dealerrank 使用：是否需要用经销商分级字段参与评分卡匹配或等级计算？</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>历史变更</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>变更内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>发现代码中选项集值（100000001/100000002）与D365实际值（10/90）不匹配，修正匹配逻辑</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>发现 mcs_accountlevel 实际值（Diamond/Gold/Silver/Other）与PRD定义（S/A/B/C/I）不匹配，建立映射关系</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>添加数据类型兼容处理（评分卡配置表: 100000000/100000001，客户标签表: 1/2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>支持同一评分项目多行分档；定量区间固定为 [min, max)；缺失/未命中取平均分；赋分允许负数；新增配置重复/重叠校验</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>备注：Parser 输出字段 → D365 评分项目编码的映射关系当前硬编码在 CofaceDataSyncPlugin 的 CofaceToD365Mapping 字典中，未存数据库；财务指标科目编码按国家从 Coface 财务指标国家配置表读取。</t>
         </is>
       </c>
     </row>
